--- a/data/4-reports/6_DOID_Matches_All.xlsx
+++ b/data/4-reports/6_DOID_Matches_All.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOID Matches (All)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matched Disease Details" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DOID Matches (All)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matched Disease Details" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DOID Matches (All)'!$A$1:$I$1</definedName>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I212"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6277,116 +6277,136 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001168</t>
+          <t>ARI:0001169</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Primary immune deficiency</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr"/>
-      <c r="D169" s="3" t="inlineStr"/>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr"/>
+          <t>Primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>DOID:0060643</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>primary sclerosing cholangitis</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>4032000</t>
+        </is>
+      </c>
       <c r="I169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001169</t>
+          <t>ARI:0001170</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>Primary sclerosing cholangitis</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>DOID:0060643</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>primary sclerosing cholangitis</t>
-        </is>
-      </c>
-      <c r="E170" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F170" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Progressive hemifacial atrophy</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr"/>
+      <c r="D170" s="3" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr"/>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>4032000</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr"/>
       <c r="I170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001170</t>
+          <t>ARI:0001171</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>Progressive hemifacial atrophy</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr"/>
-      <c r="D171" s="3" t="inlineStr"/>
-      <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" s="2" t="inlineStr"/>
+          <t>Psoriasis</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>DOID:8893</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>psoriasis</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>156369008</t>
+        </is>
+      </c>
       <c r="I171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001171</t>
+          <t>ARI:0001172</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Psoriasis</t>
+          <t>Psoriatic arthritis</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>DOID:8893</t>
+          <t>DOID:9008</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>psoriasis</t>
+          <t>psoriatic arthritis</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F172" s="2" t="inlineStr">
@@ -6401,7 +6421,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>156369008</t>
+          <t>33339001</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
@@ -6409,32 +6429,32 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001172</t>
+          <t>ARI:0001173</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>Psoriatic arthritis</t>
+          <t>Pure red cell aplasia</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>DOID:9008</t>
+          <t>DOID:1340</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>psoriatic arthritis</t>
+          <t>pure red-cell aplasia</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.549</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -6444,7 +6464,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>33339001</t>
+          <t>191252000</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -6452,32 +6472,32 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001173</t>
+          <t>ARI:0001174</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Pure red cell aplasia</t>
+          <t>Pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>DOID:1340</t>
+          <t>DOID:8553</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>pure red-cell aplasia</t>
+          <t>pyoderma gangrenosum</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>0.549</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>synonym</t>
+          <t>name</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -6487,7 +6507,7 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>191252000</t>
+          <t>74578003</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -6495,93 +6515,93 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001174</t>
+          <t>ARI:0001175</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>Pyoderma gangrenosum</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>DOID:8553</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>pyoderma gangrenosum</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Rasmussen syndrome</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr"/>
+      <c r="D175" s="3" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr"/>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>74578003</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001175</t>
+          <t>ARI:0001176</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>Rasmussen syndrome</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr"/>
-      <c r="D176" s="3" t="inlineStr"/>
-      <c r="E176" s="2" t="inlineStr"/>
-      <c r="F176" s="2" t="inlineStr"/>
+          <t>Secondary Raynaud's phenomenon</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>DOID:10300</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Raynaud disease</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H176" s="2" t="inlineStr"/>
+          <t>Raynaud disease</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>195295006</t>
+        </is>
+      </c>
       <c r="I176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001176</t>
+          <t>ARI:0001177</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>Secondary Raynaud's phenomenon</t>
+          <t>Reactive arthritis</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>DOID:10300</t>
+          <t>DOID:6196</t>
         </is>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Raynaud disease</t>
+          <t>reactive arthritis</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -6591,12 +6611,12 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>Raynaud disease</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>195295006</t>
+          <t>201506009, 266212009</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
@@ -6604,22 +6624,22 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001177</t>
+          <t>ARI:0001178</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>Reactive arthritis</t>
+          <t>Relapsing polychondritis</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>DOID:6196</t>
+          <t>DOID:2556</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>reactive arthritis</t>
+          <t>relapsing polychondritis</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -6639,7 +6659,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>201506009, 266212009</t>
+          <t>72275000</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
@@ -6647,42 +6667,42 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001178</t>
+          <t>ARI:0001179</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>Relapsing polychondritis</t>
+          <t>Restless legs</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>DOID:2556</t>
+          <t>DOID:0050425</t>
         </is>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>relapsing polychondritis</t>
+          <t>restless legs syndrome</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.549</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>synonym</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Willis-Ekbom Disease</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>72275000</t>
+          <t>32914008</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
@@ -6690,55 +6710,35 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001179</t>
+          <t>ARI:0001180</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>Restless legs</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>DOID:0050425</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>restless legs syndrome</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>0.549</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>synonym</t>
-        </is>
-      </c>
+          <t>Retinocochleocerebral vasculopathy</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr"/>
+      <c r="D180" s="3" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>Willis-Ekbom Disease</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>32914008</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001180</t>
+          <t>ARI:0001181</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>Retinocochleocerebral vasculopathy</t>
+          <t>Rheumatic Chorea</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr"/>
@@ -6756,182 +6756,202 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001181</t>
+          <t>ARI:0001182</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic Chorea</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr"/>
-      <c r="D182" s="3" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr"/>
+          <t>Rheumatic fever</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>DOID:1586</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>rheumatic fever</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>155265007, 274095001</t>
+        </is>
+      </c>
       <c r="I182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001182</t>
+          <t>ARI:0001183</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>Rheumatic fever</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>DOID:1586</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>rheumatic fever</t>
-        </is>
-      </c>
-      <c r="E183" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F183" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Rheumatoid aortitis</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr"/>
+      <c r="D183" s="3" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr"/>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="inlineStr">
-        <is>
-          <t>155265007, 274095001</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr"/>
       <c r="I183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001183</t>
+          <t>ARI:0001184</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid aortitis</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr"/>
-      <c r="D184" s="3" t="inlineStr"/>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr"/>
+          <t>Rheumatoid arthritis</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>DOID:7148</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>rheumatoid arthritis</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>156471009</t>
+        </is>
+      </c>
       <c r="I184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001184</t>
+          <t>ARI:0001185</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid arthritis</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>DOID:7148</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>rheumatoid arthritis</t>
-        </is>
-      </c>
-      <c r="E185" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F185" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Rheumatoid vasculitis</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr"/>
+      <c r="D185" s="3" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr"/>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H185" s="2" t="inlineStr">
-        <is>
-          <t>156471009</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001185</t>
+          <t>ARI:0001186</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Rheumatoid vasculitis</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr"/>
-      <c r="D186" s="3" t="inlineStr"/>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr"/>
+          <t>Sarcoidosis</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>DOID:11335</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>sarcoidosis</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>0.762</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>154425004</t>
+        </is>
+      </c>
       <c r="I186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001186</t>
+          <t>ARI:0001187</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>DOID:11335</t>
+          <t>DOID:4371</t>
         </is>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>sarcoidosis</t>
+          <t>Schnitzler syndrome</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F187" s="2" t="inlineStr">
@@ -6946,7 +6966,7 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>154425004</t>
+          <t>402415001</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
@@ -6954,27 +6974,27 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001187</t>
+          <t>ARI:0001188</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>Scleritis</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>DOID:4371</t>
+          <t>DOID:13452</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Schnitzler syndrome</t>
+          <t>scleritis</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -6989,7 +7009,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>402415001</t>
+          <t>155201000</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
@@ -6997,27 +7017,27 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001188</t>
+          <t>ARI:0001189</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>Scleritis</t>
+          <t>Sjögren's disease</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>DOID:13452</t>
+          <t>DOID:12895</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>scleritis</t>
+          <t>keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
@@ -7027,12 +7047,12 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Keratoconjunctivitis sicca</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>155201000</t>
+          <t>78946008</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
@@ -7040,22 +7060,22 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001189</t>
+          <t>ARI:0001190</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Sjögren's disease</t>
+          <t>SLE glomerulonephritis syndrome</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>DOID:12895</t>
+          <t>DOID:0080162</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>keratoconjunctivitis sicca</t>
+          <t>lupus nephritis</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -7070,35 +7090,31 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>Keratoconjunctivitis sicca</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="inlineStr">
-        <is>
-          <t>78946008</t>
-        </is>
-      </c>
+          <t>Lupus nephritis</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001190</t>
+          <t>ARI:0001191</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>SLE glomerulonephritis syndrome</t>
+          <t>Small fiber neuropathy</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>DOID:0080162</t>
+          <t>DOID:0070701</t>
         </is>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>lupus nephritis</t>
+          <t>small fiber neuropathy</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -7113,97 +7129,101 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>Lupus nephritis</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>709489006</t>
+        </is>
+      </c>
       <c r="I191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001191</t>
+          <t>ARI:0001192</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Small fiber neuropathy</t>
-        </is>
-      </c>
-      <c r="C192" s="4" t="inlineStr">
-        <is>
-          <t>DOID:0070701</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>small fiber neuropathy</t>
-        </is>
-      </c>
-      <c r="E192" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr"/>
+      <c r="D192" s="3" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr"/>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="inlineStr">
-        <is>
-          <t>709489006</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001192</t>
+          <t>ARI:0001193</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Steroid-responsive encephalopathy associated with autoimmune thyroiditis</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr"/>
-      <c r="D193" s="3" t="inlineStr"/>
-      <c r="E193" s="2" t="inlineStr"/>
-      <c r="F193" s="2" t="inlineStr"/>
+          <t>Stiff-person syndrome</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>DOID:13366</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Stiff-Person syndrome</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>5217008</t>
+        </is>
+      </c>
       <c r="I193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001193</t>
+          <t>ARI:0001194</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-person syndrome</t>
+          <t>Subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>DOID:13366</t>
+          <t>DOID:4562</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Stiff-Person syndrome</t>
+          <t>subacute bacterial endocarditis</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -7223,7 +7243,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>5217008</t>
+          <t>155334001</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -7231,22 +7251,22 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001194</t>
+          <t>ARI:0001195</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Subacute bacterial endocarditis</t>
+          <t>Sympathetic uveitis</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>DOID:4562</t>
+          <t>DOID:12029</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
         <is>
-          <t>subacute bacterial endocarditis</t>
+          <t>sympathetic ophthalmia</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -7261,12 +7281,12 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
+          <t>Sympathetic ophthalmia</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>155334001</t>
+          <t>75315001</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
@@ -7274,22 +7294,22 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001195</t>
+          <t>ARI:0001196</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic uveitis</t>
+          <t>Systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>DOID:12029</t>
+          <t>DOID:9074</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>sympathetic ophthalmia</t>
+          <t>systemic lupus erythematosus</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -7304,12 +7324,12 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>Sympathetic ophthalmia</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>75315001</t>
+          <t>156450004</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
@@ -7317,93 +7337,93 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001196</t>
+          <t>ARI:0001197</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Systemic lupus erythematosus</t>
-        </is>
-      </c>
-      <c r="C197" s="4" t="inlineStr">
-        <is>
-          <t>DOID:9074</t>
-        </is>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>systemic lupus erythematosus</t>
-        </is>
-      </c>
-      <c r="E197" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F197" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Systemic mast cell disease</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr"/>
+      <c r="D197" s="3" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H197" s="2" t="inlineStr">
-        <is>
-          <t>156450004</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001197</t>
+          <t>ARI:0001198</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Systemic mast cell disease</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="inlineStr"/>
-      <c r="D198" s="3" t="inlineStr"/>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr"/>
+          <t>Systemic sclerosis</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>DOID:418</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>systemic scleroderma</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="inlineStr"/>
+          <t>Systemic scleroderma</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>89155008</t>
+        </is>
+      </c>
       <c r="I198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001198</t>
+          <t>ARI:0001199</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis</t>
+          <t>Systemic sclerosis with limited cutaneous involvement</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>DOID:418</t>
+          <t>DOID:0060218</t>
         </is>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>systemic scleroderma</t>
+          <t>CREST syndrome</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -7413,12 +7433,12 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>Systemic scleroderma</t>
+          <t>CREST syndrome</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>89155008</t>
+          <t>31848007, 62382002</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
@@ -7426,22 +7446,22 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001199</t>
+          <t>ARI:0001200</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Systemic sclerosis with limited cutaneous involvement</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>DOID:0060218</t>
+          <t>DOID:2508</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>CREST syndrome</t>
+          <t>Takayasu's arteritis</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -7456,12 +7476,12 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>CREST syndrome</t>
+          <t>(preferred name)</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>31848007, 62382002</t>
+          <t>359789008, 42153001</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -7469,27 +7489,27 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001200</t>
+          <t>ARI:0001201</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>Temporal arteritis</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>DOID:2508</t>
+          <t>DOID:13375</t>
         </is>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Takayasu's arteritis</t>
+          <t>temporal arteritis</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -7504,7 +7524,7 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>359789008, 42153001</t>
+          <t>195354005</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr"/>
@@ -7512,88 +7532,88 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001201</t>
+          <t>ARI:0001202</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Temporal arteritis</t>
-        </is>
-      </c>
-      <c r="C202" s="4" t="inlineStr">
-        <is>
-          <t>DOID:13375</t>
-        </is>
-      </c>
-      <c r="D202" s="3" t="inlineStr">
-        <is>
-          <t>temporal arteritis</t>
-        </is>
-      </c>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F202" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>TIF1-gamma positive dermatomyositis</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr"/>
+      <c r="D202" s="3" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr"/>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H202" s="2" t="inlineStr">
-        <is>
-          <t>195354005</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001202</t>
+          <t>ARI:0001203</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>TIF1-gamma positive dermatomyositis</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr"/>
-      <c r="D203" s="3" t="inlineStr"/>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr"/>
+          <t>Tolosa-Hunt syndrome</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>DOID:1278</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>tolosa-hunt syndrome</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H203" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>75111000</t>
+        </is>
+      </c>
       <c r="I203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001203</t>
+          <t>ARI:0001204</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Tolosa-Hunt syndrome</t>
+          <t>Transverse myelitis</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>DOID:1278</t>
+          <t>DOID:0080743</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>tolosa-hunt syndrome</t>
+          <t>transverse myelitis</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -7611,32 +7631,28 @@
           <t>(preferred name)</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
-        <is>
-          <t>75111000</t>
-        </is>
-      </c>
+      <c r="H204" s="2" t="inlineStr"/>
       <c r="I204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001204</t>
+          <t>ARI:0001205</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Transverse myelitis</t>
+          <t>Ulcerative colitis</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>DOID:0080743</t>
+          <t>DOID:8577</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>transverse myelitis</t>
+          <t>ulcerative colitis</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -7654,61 +7670,45 @@
           <t>(preferred name)</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>196988003, 441971007</t>
+        </is>
+      </c>
       <c r="I205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001205</t>
+          <t>ARI:0001206</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Ulcerative colitis</t>
-        </is>
-      </c>
-      <c r="C206" s="4" t="inlineStr">
-        <is>
-          <t>DOID:8577</t>
-        </is>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>ulcerative colitis</t>
-        </is>
-      </c>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="F206" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Undifferentiated connective tissue disease</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr"/>
+      <c r="D206" s="3" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H206" s="2" t="inlineStr">
-        <is>
-          <t>196988003, 441971007</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr"/>
       <c r="I206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001206</t>
+          <t>ARI:0001207</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>Undifferentiated connective tissue disease</t>
+          <t>Urticarial vasculitis</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr"/>
@@ -7726,21 +7726,37 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001207</t>
+          <t>ARI:0001208</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Urticarial vasculitis</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr"/>
-      <c r="D208" s="3" t="inlineStr"/>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr"/>
+          <t>Uveitis</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>DOID:0040088</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>autoimmune uveitis</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>0.772</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>no match</t>
+          <t>Autoimmune uveitis</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
@@ -7749,27 +7765,27 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001208</t>
+          <t>ARI:0001209</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>Uveitis</t>
+          <t>Vitiligo</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>DOID:0040088</t>
+          <t>DOID:12306</t>
         </is>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>autoimmune uveitis</t>
+          <t>vitiligo</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.762</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -7779,36 +7795,40 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>Autoimmune uveitis</t>
-        </is>
-      </c>
-      <c r="H209" s="2" t="inlineStr"/>
+          <t>(preferred name)</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>156437000</t>
+        </is>
+      </c>
       <c r="I209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001209</t>
+          <t>ARI:0001210</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>DOID:12306</t>
+          <t>DOID:12297</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>vitiligo</t>
+          <t>Vogt-Koyanagi-Harada disease</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -7823,7 +7843,7 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>156437000</t>
+          <t>44923005</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
@@ -7831,68 +7851,25 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ARI:0001210</t>
+          <t>ARI:0001211</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>DOID:12297</t>
-        </is>
-      </c>
-      <c r="D211" s="3" t="inlineStr">
-        <is>
-          <t>Vogt-Koyanagi-Harada disease</t>
-        </is>
-      </c>
-      <c r="E211" s="2" t="inlineStr">
-        <is>
-          <t>0.778</t>
-        </is>
-      </c>
-      <c r="F211" s="2" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>Warm autoimmune hemolytic anemia</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr"/>
+      <c r="D211" s="3" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr"/>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>(preferred name)</t>
-        </is>
-      </c>
-      <c r="H211" s="2" t="inlineStr">
-        <is>
-          <t>44923005</t>
-        </is>
-      </c>
+          <t>no match</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr"/>
       <c r="I211" s="2" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
-        <is>
-          <t>ARI:0001211</t>
-        </is>
-      </c>
-      <c r="B212" s="3" t="inlineStr">
-        <is>
-          <t>Warm autoimmune hemolytic anemia</t>
-        </is>
-      </c>
-      <c r="C212" s="2" t="inlineStr"/>
-      <c r="D212" s="3" t="inlineStr"/>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>no match</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -7996,37 +7973,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId130"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8303,12 +8280,12 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M30.3; ICD9CM:446.1</t>
+          <t>ICD10CM:M30.3</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004246; GARD:6816; MIM:611775</t>
+          <t>EFO:0004246; GARD:6816; ICD9CM:446.1; MIM:611775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
@@ -8495,12 +8472,12 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H35.30; ICD9CM:362.50</t>
+          <t>ICD10CM:H35.30</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>EFO:0001365; MIM:PS603075</t>
+          <t>EFO:0001365; ICD9CM:362.50; MIM:PS603075</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
@@ -8555,12 +8532,12 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L63; ICD9CM:704.01</t>
+          <t>ICD10CM:L63</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004192; GARD:5782; MIM:104000; MIM:610753</t>
+          <t>EFO:0004192; GARD:5782; ICD9CM:704.01; MIM:104000; MIM:610753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
@@ -8683,12 +8660,12 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M45; ICD9CM:720.0</t>
+          <t>ICD10CM:M45</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>EFO:0003898; GARD:9518; MIM:PS106300; ORDO:825</t>
+          <t>EFO:0003898; GARD:9518; ICD9CM:720.0; MIM:PS106300; ORDO:825</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
@@ -8747,12 +8724,12 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M31.0; ICD9CM:446.21</t>
+          <t>ICD10CM:M31.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>GARD:2551; MIM:233450</t>
+          <t>GARD:2551; ICD9CM:446.21; MIM:233450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
@@ -8915,12 +8892,12 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:D61.9; ICD9CM:284.9</t>
+          <t>ICD10CM:D61.9</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>GARD:5836; MIM:609135</t>
+          <t>GARD:5836; ICD9CM:284.9; MIM:609135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
@@ -8965,14 +8942,10 @@
           <t>UMLS_CUI:C0003089</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>ICD9CM:720</t>
-        </is>
-      </c>
+      <c r="L15" s="3" t="inlineStr"/>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>MIM:109100</t>
+          <t>ICD9CM:720; MIM:109100</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
@@ -9031,12 +9004,12 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H81.0; ICD9CM:386.0</t>
+          <t>ICD10CM:H81.0</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>GARD:10340; MIM:156000</t>
+          <t>GARD:10340; ICD9CM:386.0; MIM:156000</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
@@ -9129,14 +9102,10 @@
           <t>UMLS_CUI:C0002880</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>ICD9CM:283.0</t>
-        </is>
-      </c>
+      <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>GARD:5870; MIM:205700</t>
+          <t>GARD:5870; ICD9CM:283.0; MIM:205700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
@@ -9193,14 +9162,10 @@
           <t>UMLS_CUI:C0241910; UMLS_CUI:C1332355</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>ICD9CM:571.42</t>
-        </is>
-      </c>
+      <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>GARD:5871</t>
+          <t>GARD:5871; ICD9CM:571.42</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr"/>
@@ -9259,12 +9224,12 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:D89.82; ICD9CM:279.41</t>
+          <t>ICD10CM:D89.82</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>GARD:8686; MIM:601859; ORDO:3261</t>
+          <t>GARD:8686; ICD9CM:279.41; MIM:601859; ORDO:3261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
@@ -9515,12 +9480,12 @@
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G37.0; ICD9CM:341.1</t>
+          <t>ICD10CM:G37.0</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>GARD:5885</t>
+          <t>GARD:5885; ICD9CM:341.1</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
@@ -9583,12 +9548,12 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M35.2; ICD9CM:136.1</t>
+          <t>ICD10CM:M35.2</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>EFO:0003780; GARD:848; MIM:109650</t>
+          <t>EFO:0003780; GARD:848; ICD9CM:136.1; MIM:109650</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
@@ -9647,12 +9612,12 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L12.1; ICD9CM:694.6; ICD9CM:694.61</t>
+          <t>ICD10CM:L12.1</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>GARD:5913; MIM:164185</t>
+          <t>GARD:5913; ICD9CM:694.6; ICD9CM:694.61; MIM:164185</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
@@ -9763,12 +9728,12 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L12.0; ICD9CM:694.5</t>
+          <t>ICD10CM:L12.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>GARD:5972</t>
+          <t>GARD:5972; ICD9CM:694.5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
@@ -9827,12 +9792,12 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:K90.0; ICD9CM:579.0</t>
+          <t>ICD10CM:K90.0</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>EFO:0001060; GARD:11998; MIM:607202; MIM:609754; MIM:611598; MIM:612005; MIM:612006; MIM:612007; MIM:612008; MIM:612009; MIM:612011; ORDO:555</t>
+          <t>EFO:0001060; GARD:11998; ICD9CM:579.0; MIM:607202; MIM:609754; MIM:611598; MIM:612005; MIM:612006; MIM:612007; MIM:612008; MIM:612009; MIM:612011; ORDO:555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
@@ -9891,12 +9856,12 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G93.32; ICD9CM:780.71</t>
+          <t>ICD10CM:G93.32</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>GARD:7121</t>
+          <t>GARD:7121; ICD9CM:780.71</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
@@ -9951,12 +9916,12 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G61.81; ICD9CM:357.81</t>
+          <t>ICD10CM:G61.81</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>GARD:6102</t>
+          <t>GARD:6102; ICD9CM:357.81</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
@@ -10007,10 +9972,14 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:N30.1; ICD9CM:595.1</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
+          <t>ICD10CM:N30.1</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:595.1</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
@@ -10067,12 +10036,12 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:A69.2; ICD9CM:088.81</t>
+          <t>ICD10CM:A69.2</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>GARD:12073</t>
+          <t>GARD:12073; ICD9CM:088.81</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
@@ -10207,10 +10176,14 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H16.32; ICD9CM:370.52</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
+          <t>ICD10CM:H16.32</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:370.52</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -10367,12 +10340,12 @@
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:K50.1; ICD9CM:555.1</t>
+          <t>ICD10CM:K50.1</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000384; GARD:10232</t>
+          <t>EFO:0000384; GARD:10232; ICD9CM:555.1</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr"/>
@@ -10435,10 +10408,14 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:J84.114; ICD9CM:516.33</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
+          <t>ICD10CM:J84.114</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:516.33</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -10591,12 +10568,12 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L13.0; ICD9CM:694.0</t>
+          <t>ICD10CM:L13.0</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>GARD:1917</t>
+          <t>GARD:1917; ICD9CM:694.0</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr"/>
@@ -10659,12 +10636,12 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M33; ICD9CM:710.3</t>
+          <t>ICD10CM:M33</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>GARD:6263</t>
+          <t>GARD:6263; ICD9CM:710.3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr"/>
@@ -10787,10 +10764,14 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G70.80; ICD9CM:358.3</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="inlineStr"/>
+          <t>ICD10CM:G70.80</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:358.3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -10843,12 +10824,12 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:N80; ICD9CM:617</t>
+          <t>ICD10CM:N80</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>EFO:0001065</t>
+          <t>EFO:0001065; ICD9CM:617</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr"/>
@@ -10903,12 +10884,12 @@
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:K20.0; ICD9CM:530.13</t>
+          <t>ICD10CM:K20.0</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004232; MIM:610247; MIM:613412; ORDO:73247</t>
+          <t>EFO:0004232; ICD9CM:530.13; MIM:610247; MIM:613412; ORDO:73247</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr"/>
@@ -10967,12 +10948,12 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G40.909; ICD9CM:345.9</t>
+          <t>ICD10CM:G40.909</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000474</t>
+          <t>EFO:0000474; ICD9CM:345.9</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr"/>
@@ -11071,12 +11052,12 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M05.0; ICD9CM:714.1</t>
+          <t>ICD10CM:M05.0</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>GARD:8234; MIM:134750</t>
+          <t>GARD:8234; ICD9CM:714.1; MIM:134750</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
@@ -11443,12 +11424,12 @@
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M31.0; ICD9CM:446.2</t>
+          <t>ICD10CM:M31.0</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>GARD:7851</t>
+          <t>GARD:7851; ICD9CM:446.2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
@@ -11507,12 +11488,12 @@
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:J84.112; ICD9CM:516.31</t>
+          <t>ICD10CM:J84.112</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000768; GARD:8609</t>
+          <t>EFO:0000768; GARD:8609; ICD9CM:516.31</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr"/>
@@ -11635,12 +11616,12 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:D69.3; ICD9CM:287.31</t>
+          <t>ICD10CM:D69.3</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>MIM:188030</t>
+          <t>ICD9CM:287.31; MIM:188030</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr"/>
@@ -11699,12 +11680,12 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:D69.0; ICD9CM:287.0</t>
+          <t>ICD10CM:D69.0</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>GARD:8204; ORDO:761</t>
+          <t>GARD:8204; ICD9CM:287.0; ORDO:761</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr"/>
@@ -11799,12 +11780,12 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G72.41; ICD9CM:359.71</t>
+          <t>ICD10CM:G72.41</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>GARD:3896; MIM:147421; ORDO:611</t>
+          <t>GARD:3896; ICD9CM:359.71; MIM:147421; ORDO:611</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr"/>
@@ -12079,12 +12060,12 @@
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M08.4; ICD9CM:714.3; ICD9CM:714.31; ICD9CM:714.32; ICD9CM:714.33</t>
+          <t>ICD10CM:M08.4</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>GARD:3067; MIM:604302; ORDO:92</t>
+          <t>GARD:3067; ICD9CM:714.3; ICD9CM:714.31; ICD9CM:714.32; ICD9CM:714.33; MIM:604302; ORDO:92</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr"/>
@@ -12143,12 +12124,12 @@
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L43; ICD9CM:697.0</t>
+          <t>ICD10CM:L43</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>GARD:12344</t>
+          <t>GARD:12344; ICD9CM:697.0</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
@@ -12201,12 +12182,12 @@
           <t>UMLS_CUI:C0152460</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr"/>
+      <c r="M71" s="3" t="inlineStr">
         <is>
           <t>ICD9CM:607.81</t>
         </is>
       </c>
-      <c r="M71" s="3" t="inlineStr"/>
       <c r="N71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
@@ -12487,10 +12468,14 @@
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H16.05; ICD9CM:370.07</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="inlineStr"/>
+          <t>ICD10CM:H16.05</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:370.07</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
@@ -12543,12 +12528,12 @@
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L94.0; ICD9CM:701.0</t>
+          <t>ICD10CM:L94.0</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>GARD:7058</t>
+          <t>GARD:7058; ICD9CM:701.0</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr"/>
@@ -12607,12 +12592,12 @@
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:I67.5; ICD9CM:437.5</t>
+          <t>ICD10CM:I67.5</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>GARD:7064; MIM:252350; MIM:300845; MIM:607151; MIM:608796; MIM:614042; MIM:615750; ORDO:2573; ORDO:280679; ORDO:401945</t>
+          <t>GARD:7064; ICD9CM:437.5; MIM:252350; MIM:300845; MIM:607151; MIM:608796; MIM:614042; MIM:615750; ORDO:2573; ORDO:280679; ORDO:401945</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr"/>
@@ -12671,12 +12656,12 @@
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G35; ICD9CM:340</t>
+          <t>ICD10CM:G35</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>GARD:10255; MIM:612594; MIM:612595; MIM:612596</t>
+          <t>GARD:10255; ICD9CM:340; MIM:612594; MIM:612595; MIM:612596</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr"/>
@@ -12731,12 +12716,12 @@
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G70.0; ICD10CM:G70.00; ICD9CM:358.0; ICD9CM:358.00</t>
+          <t>ICD10CM:G70.0; ICD10CM:G70.00</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>GARD:7122; MIM:254200</t>
+          <t>GARD:7122; ICD9CM:358.0; ICD9CM:358.00; MIM:254200</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr"/>
@@ -12955,12 +12940,12 @@
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G36.0; ICD9CM:341.0</t>
+          <t>ICD10CM:G36.0</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004256; GARD:6267</t>
+          <t>EFO:0004256; GARD:6267; ICD9CM:341.0</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
@@ -13059,12 +13044,12 @@
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M12.3; ICD9CM:719.3; ICD9CM:719.31</t>
+          <t>ICD10CM:M12.3</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
-          <t>GARD:7304</t>
+          <t>GARD:7304; ICD9CM:719.3; ICD9CM:719.31</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
@@ -13267,12 +13252,12 @@
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L10; ICD9CM:694.4</t>
+          <t>ICD10CM:L10</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
-          <t>GARD:7352</t>
+          <t>GARD:7352; ICD9CM:694.4</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr"/>
@@ -13383,12 +13368,12 @@
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M30.0; ICD9CM:446.0</t>
+          <t>ICD10CM:M30.0</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>GARD:7360</t>
+          <t>GARD:7360; ICD9CM:446.0</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr"/>
@@ -13547,10 +13532,14 @@
       </c>
       <c r="L95" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M35.3; ICD9CM:725</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr"/>
+          <t>ICD10CM:M35.3</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:725</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
@@ -13643,10 +13632,14 @@
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:I24.1; ICD9CM:411.0</t>
-        </is>
-      </c>
-      <c r="M97" s="3" t="inlineStr"/>
+          <t>ICD10CM:I24.1</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:411.0</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
@@ -13755,12 +13748,12 @@
       </c>
       <c r="L99" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:K74.3; ICD10CM:K74.5; ICD9CM:571.6</t>
+          <t>ICD10CM:K74.3; ICD10CM:K74.5</t>
         </is>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004267; GARD:7459; MIM:PS109720; ORDO:186</t>
+          <t>EFO:0004267; GARD:7459; ICD9CM:571.6; MIM:PS109720; ORDO:186</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr"/>
@@ -14011,12 +14004,12 @@
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L40.5; ICD9CM:696.0</t>
+          <t>ICD10CM:L40.5</t>
         </is>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
-          <t>EFO:0003778</t>
+          <t>EFO:0003778; ICD9CM:696.0</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr"/>
@@ -14123,12 +14116,12 @@
       </c>
       <c r="L105" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L88; ICD9CM:686.01</t>
+          <t>ICD10CM:L88</t>
         </is>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>GARD:7510</t>
+          <t>GARD:7510; ICD9CM:686.01</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr"/>
@@ -14183,12 +14176,12 @@
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:I73.0; ICD9CM:443.0</t>
+          <t>ICD10CM:I73.0</t>
         </is>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>MIM:179600</t>
+          <t>ICD9CM:443.0; MIM:179600</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr"/>
@@ -14247,12 +14240,12 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M02.10; ICD10CM:M02.3; ICD9CM:099.3; ICD9CM:711.30</t>
+          <t>ICD10CM:M02.10; ICD10CM:M02.3</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>GARD:5693</t>
+          <t>GARD:5693; ICD9CM:099.3; ICD9CM:711.30</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr"/>
@@ -14375,12 +14368,12 @@
       </c>
       <c r="L109" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G25.81; ICD9CM:333.94</t>
+          <t>ICD10CM:G25.81</t>
         </is>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004270; GARD:11926; MIM:PS102300</t>
+          <t>EFO:0004270; GARD:11926; ICD9CM:333.94; MIM:PS102300</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr"/>
@@ -14439,12 +14432,12 @@
       </c>
       <c r="L110" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:I00; ICD10CM:I00-I02; ICD9CM:390; ICD9CM:390-392.99</t>
+          <t>ICD10CM:I00; ICD10CM:I00-I02</t>
         </is>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
-          <t>GARD:5699</t>
+          <t>GARD:5699; ICD9CM:390; ICD9CM:390-392.99</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr"/>
@@ -14503,12 +14496,12 @@
       </c>
       <c r="L111" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M06.9; ICD9CM:714.0</t>
+          <t>ICD10CM:M06.9</t>
         </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000685; KEGG:05323; MIM:180300</t>
+          <t>EFO:0000685; ICD9CM:714.0; KEGG:05323; MIM:180300</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr"/>
@@ -14567,12 +14560,12 @@
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:D86; ICD9CM:135</t>
+          <t>ICD10CM:D86</t>
         </is>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>GARD:7607; ORDO:797</t>
+          <t>GARD:7607; ICD9CM:135; ORDO:797</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr"/>
@@ -14675,12 +14668,12 @@
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H15.0; ICD9CM:379.00</t>
+          <t>ICD10CM:H15.0</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>GARD:12911</t>
+          <t>GARD:12911; ICD9CM:379.00</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr"/>
@@ -14891,12 +14884,12 @@
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:G25.82; ICD9CM:333.91</t>
+          <t>ICD10CM:G25.82</t>
         </is>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
-          <t>GARD:5023; MIM:184850</t>
+          <t>GARD:5023; ICD9CM:333.91; MIM:184850</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr"/>
@@ -15003,10 +14996,14 @@
       </c>
       <c r="L120" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H44.13; ICD9CM:360.11</t>
-        </is>
-      </c>
-      <c r="M120" s="3" t="inlineStr"/>
+          <t>ICD10CM:H44.13</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>ICD9CM:360.11</t>
+        </is>
+      </c>
       <c r="N120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
@@ -15063,12 +15060,12 @@
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M32.9; ICD9CM:710.0</t>
+          <t>ICD10CM:M32.9</t>
         </is>
       </c>
       <c r="M121" s="3" t="inlineStr">
         <is>
-          <t>GARD:10253; KEGG:05322; MIM:152700; MIM:300809; MIM:605480; MIM:608437; MIM:609903; MIM:609939; MIM:610065; MIM:610066; MIM:612254; MIM:612378; MIM:613145; MIM:614420; ORDO:536</t>
+          <t>GARD:10253; ICD9CM:710.0; KEGG:05322; MIM:152700; MIM:300809; MIM:605480; MIM:608437; MIM:609903; MIM:609939; MIM:610065; MIM:610066; MIM:612254; MIM:612378; MIM:613145; MIM:614420; ORDO:536</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr"/>
@@ -15127,12 +15124,12 @@
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M34.0; ICD9CM:710.1</t>
+          <t>ICD10CM:M34.0</t>
         </is>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000717; GARD:9748; MIM:181750</t>
+          <t>EFO:0000717; GARD:9748; ICD9CM:710.1; MIM:181750</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr"/>
@@ -15251,12 +15248,12 @@
       </c>
       <c r="L124" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:M31.4; ICD9CM:446.7</t>
+          <t>ICD10CM:M31.4</t>
         </is>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>GARD:7730; MIM:207600</t>
+          <t>GARD:7730; ICD9CM:446.7; MIM:207600</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr"/>
@@ -15313,14 +15310,10 @@
           <t>UMLS_CUI:C0039483</t>
         </is>
       </c>
-      <c r="L125" s="3" t="inlineStr">
-        <is>
-          <t>ICD9CM:446.5</t>
-        </is>
-      </c>
+      <c r="L125" s="3" t="inlineStr"/>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>MIM:187360; ORDO:397</t>
+          <t>ICD9CM:446.5; MIM:187360; ORDO:397</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr"/>
@@ -15467,12 +15460,12 @@
       </c>
       <c r="L128" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:K51; ICD9CM:556; ICD9CM:556.5</t>
+          <t>ICD10CM:K51</t>
         </is>
       </c>
       <c r="M128" s="3" t="inlineStr">
         <is>
-          <t>EFO:0000729</t>
+          <t>EFO:0000729; ICD9CM:556; ICD9CM:556.5</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr"/>
@@ -15563,12 +15556,12 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:L80; ICD9CM:709.01</t>
+          <t>ICD10CM:L80</t>
         </is>
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>EFO:0004208; GARD:10751; MIM:193200</t>
+          <t>EFO:0004208; GARD:10751; ICD9CM:709.01; MIM:193200</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr"/>
@@ -15627,12 +15620,12 @@
       </c>
       <c r="L131" s="3" t="inlineStr">
         <is>
-          <t>ICD10CM:H20.82; ICD9CM:364.24</t>
+          <t>ICD10CM:H20.82</t>
         </is>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>GARD:7862</t>
+          <t>GARD:7862; ICD9CM:364.24</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr"/>
